--- a/output/pdf_financials_xlsx/SUU.xlsx
+++ b/output/pdf_financials_xlsx/SUU.xlsx
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.178634</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.423949</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.805606</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.399441</v>
       </c>
     </row>
     <row r="93">
@@ -3586,7 +3586,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3910,7 +3914,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>1.178634</v>
       </c>

--- a/output/pdf_financials_xlsx/SUU.xlsx
+++ b/output/pdf_financials_xlsx/SUU.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.043743</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.121594</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.047613</v>
       </c>
     </row>
     <row r="13">
@@ -967,13 +967,13 @@
         <v>-1.292309</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.928639</v>
+        <v>-3.972382</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.720359</v>
+        <v>-3.841953</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.848294</v>
+        <v>-1.895907</v>
       </c>
     </row>
     <row r="28">
@@ -1005,13 +1005,13 @@
         <v>-1.292309</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.928639</v>
+        <v>-3.972382</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.720359</v>
+        <v>-3.841953</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.848294</v>
+        <v>-1.895907</v>
       </c>
     </row>
     <row r="30">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">

--- a/output/pdf_financials_xlsx/SUU.xlsx
+++ b/output/pdf_financials_xlsx/SUU.xlsx
@@ -2394,16 +2394,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000587</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.036161</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.08848</v>
+        <v>-0.151709</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.08848</v>
+        <v>0.170928</v>
       </c>
     </row>
     <row r="102">
@@ -2489,16 +2489,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.194688</v>
+        <v>0.195275</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.165532</v>
+        <v>-0.201693</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.082874</v>
+        <v>-0.146103</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.112307</v>
+        <v>0.194755</v>
       </c>
     </row>
     <row r="107">
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.037404</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.08082</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.08268399999999999</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -4308,7 +4308,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.000587</v>
       </c>
@@ -4896,7 +4900,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.037404</v>
       </c>
@@ -5316,7 +5324,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>1.034</v>
       </c>
